--- a/data/seed/portfolio/L-2025-8940/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-8940/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I168"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -558,23 +558,23 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>3313000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>15431000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -584,14 +584,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Shartnoma №147/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №9/26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -601,38 +601,38 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>10140000</v>
+        <v>36444000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №254/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7962</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -640,40 +640,40 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>5866000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>7700000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omad Dori-Darmon MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>263369653</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000352017875001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7294</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6137 02.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -681,40 +681,40 @@
           <t>103</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>13915000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>3212000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №5439</t>
+          <t>SHARTNOMA №277/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -722,40 +722,40 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>52035000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>12210000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Olmaliq Tikuv MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>324142150</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000896637623001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №180/26 от 06.07.2026</t>
+          <t>Оплата за сырье по договору №247/26 от 03.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -763,33 +763,33 @@
           <t>105</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>36343000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>24975000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Qo'qon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>353385283</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000551531057001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №4450</t>
+          <t>Tovarlar uchun to'lov h/f №5967</t>
         </is>
       </c>
     </row>
@@ -806,21 +806,21 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>26347000</v>
+        <v>17852000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №268 06.07.2026, QQS bilan</t>
+          <t>Yetkazigan tovar uchun to'lov h/f №702</t>
         </is>
       </c>
     </row>
@@ -847,31 +847,31 @@
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>9338000</v>
+        <v>9926000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Shartnoma №119/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №48/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -888,31 +888,31 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>8947000</v>
+        <v>2735000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8935</t>
+          <t>Shartnoma №201/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -927,40 +927,35 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>5225000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>35285000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>353047245</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2934 06.07.2026, QQS bilan</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -970,21 +965,21 @@
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>3830000</v>
+        <v>4269000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -994,14 +989,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №237/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №225/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1009,40 +1004,40 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>10481000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>19348000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qo'qon Non MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>298553382</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000217624148001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4873</t>
+          <t>Оплата за товар по счет-фактуре №878 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1051,34 +1046,39 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>35285000</v>
+        <v>9824000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ISH HAQI TO'LOVI IYUN 2026 (PLASTIK KARTALARGA)</t>
+          <t>Предоплата за материалы по договору №185/26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1092,27 +1092,27 @@
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Buxoro Qurilish Materiallari XK</t>
+          <t>Marg'ilon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>273362210</t>
+          <t>373800074</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000002946212001</t>
+          <t>20208000143983689001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Арендная плата за июль 2026 г. по договору №63/21</t>
         </is>
       </c>
     </row>
@@ -1127,40 +1127,40 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>9383000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>23082000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Olmaliq Tikuv MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>324142150</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000896637623001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9457 09.07.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №9971</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,23 +1168,23 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>11409000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>12627000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Omad Dori-Darmon MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>263369653</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000352017875001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №84/26</t>
+          <t>Предоплата за товар по дог. №86/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1211,38 +1211,38 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>5783000</v>
+        <v>5402000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>300914599</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000769064736001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1747 10.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №262/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1252,21 +1252,21 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>3712000</v>
+        <v>4132000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1276,14 +1276,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5352 10.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №208/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1293,38 +1293,38 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>3503000</v>
+        <v>2518000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Omad Agro Servis MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>353455094</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000115493186001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4492</t>
+          <t>Оплата по счет-фактуре №4010 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1334,21 +1334,21 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>11392000</v>
+        <v>39859000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1358,14 +1358,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №27/26 от 13.07.2026</t>
+          <t>Оплата за продукцию по договору №44/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1375,21 +1375,21 @@
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>8003000</v>
+        <v>7048000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1399,14 +1399,14 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2289 13.07.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5237</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1416,38 +1416,38 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>5801000</v>
+        <v>2557000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №179/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №1373 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1455,40 +1455,40 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>3977000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>11646000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Olmaliq Tikuv MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>324142150</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000896637623001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8095 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №49/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1497,39 +1497,39 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8696000</v>
+        <v>19976000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTN. №217/26, QQS BILAN</t>
+          <t>Оплата за товары согласно с/ф №2942</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1538,39 +1538,34 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>10207000</v>
+        <v>37900000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>356873558</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-8940)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>16307000367732556417</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №13/26</t>
+          <t>Kredit shartnomasi L-2025-8940 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1578,23 +1573,23 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>20690000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>3030000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Omad Dori-Darmon MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>263369653</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000352017875001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1604,14 +1599,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №279/26</t>
+          <t>Tovar uchun to'lov, h/f №95 16.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1619,40 +1614,40 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>21145000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>2537000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №244/26</t>
+          <t>Предоплата за товар по договору №92/26 от 16.07.2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1661,39 +1656,39 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>22016000</v>
+        <v>4812000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nukus Trans Servis XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>238308997</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000489728766001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №8/26</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1701,40 +1696,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>5963000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>4812000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Omad Agro Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>353455094</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000115493186001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №29/26, QQS 12%</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1743,39 +1738,39 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>10832000</v>
+        <v>4822000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nukus Trans Servis XK</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>238308997</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000489728766001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №142/26</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №82/26 ОТ 16.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1784,34 +1779,39 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>37900000</v>
+        <v>5339000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-8940)</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>16307000367732556417</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-8940 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за товары согласно с/ф №5134</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,40 +1819,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>4812000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>11179000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Предоплата за товар по договору №167/26 от 17.07.2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1861,39 +1861,39 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>4812000</v>
+        <v>37583000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>JSHDS IYUN OYI UCHUN</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №232/26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1901,40 +1901,40 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>11305000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>70860000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Omad Dori-Darmon MChJ</t>
+          <t>Buxoro Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>263369653</t>
+          <t>227530375</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000352017875001</t>
+          <t>20208000480405571001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №200/26</t>
+          <t>Предоплата за товар по дог. №216/26 от 20.07.2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1944,38 +1944,38 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>34950000</v>
+        <v>7203000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>335820015</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000828621740001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Shartnoma №53/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по с/ф №9248 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,38 +1985,38 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>21571000</v>
+        <v>3554000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Bahor Moy MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>377611030</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000165686910001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6829 17.07.2026, QQS bilan</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №263 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>11124000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>5265000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №240/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №111/26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,23 +2065,23 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>6958000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>8478000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2018 17.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №3518</t>
         </is>
       </c>
     </row>
@@ -2106,40 +2106,40 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>4350000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>15318000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Olmaliq Tikuv MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>324142150</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000896637623001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №286/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №62/26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2149,38 +2149,38 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>3406000</v>
+        <v>33994000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Oydin Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>245509421</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000549318625001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Shartnoma №42/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №246/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2189,22 +2189,22 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>6319000</v>
+        <v>53963000</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2214,14 +2214,14 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №143/26</t>
+          <t>Оплата за транспортные услуги по дог. №287/26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2229,40 +2229,40 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>11806000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>5947000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Shodlik Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>382001558</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000862174052001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №91/26</t>
+          <t>Предоплата за товар по договору №209/26 от 23.07.2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>5024000</v>
+        <v>4765000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
@@ -2296,14 +2296,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2313,21 +2313,21 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>3713000</v>
+        <v>26029000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>387355810</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000736865572001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2337,14 +2337,14 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору 81/26, НДС 12%</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №22/26 ОТ 27.07.2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2354,38 +2354,38 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>3087000</v>
+        <v>10650000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>300914599</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000769064736001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5199 от 24.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №56/26 от 27.07.2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2394,32 +2394,32 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>16001000</v>
+        <v>1880000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nukus Trans Servis XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>238308997</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000489728766001</t>
+          <t>20208000654034012001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №78/26, QQS BILAN</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
     </row>
@@ -2434,33 +2434,33 @@
           <t>146</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>4282000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>15062000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Shartnoma №164/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №9765</t>
         </is>
       </c>
     </row>
@@ -2476,39 +2476,39 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>1880000</v>
+        <v>17645000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000042275412001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №172/26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2516,40 +2516,40 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>9776000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>8546000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oqtosh Metall MChJ</t>
+          <t>Oydin Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>357211150</t>
+          <t>245509421</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000420711962001</t>
+          <t>20208000549318625001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4073</t>
+          <t>Оплата по счет-фактуре №3057 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2557,40 +2557,40 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>9792000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>5383000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №292/26 от 27.07.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №68 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2598,40 +2598,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>11040000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>5296000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Omad Dori-Darmon MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>263369653</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000352017875001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №117/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №53/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2639,40 +2639,40 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>11549000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>2483000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №16/26</t>
+          <t>Предоплата за товар по договору №182/26 от 29.07.2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2681,32 +2681,32 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>28530000</v>
+        <v>4664000</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №207/26</t>
+          <t>Оплата за сырье по договору №250/26 от 29.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2721,40 +2721,40 @@
           <t>153</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>68755000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>19017000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7870 от 29.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №236/26 от 29.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2764,21 +2764,21 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>18466000</v>
+        <v>16926000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>387355810</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000736865572001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2788,14 +2788,14 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2851</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6773</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2805,38 +2805,38 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>4658000</v>
+        <v>7820000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>335820015</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000828621740001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6554</t>
+          <t>Предоплата за товар по договору №278/26 от 31.07.2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2845,32 +2845,27 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>72045000</v>
+        <v>300000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>356873558</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №140/26 от 30.07.2026, НДС 12%</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
@@ -2885,40 +2880,40 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>6661000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>7210000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Shartnoma №173/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №623</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2928,21 +2923,21 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>4774000</v>
+        <v>79113000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2952,14 +2947,14 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №4739 31.07.2026, QQS BILAN</t>
+          <t>Оплата за товар по счет-фактуре №6809 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2969,38 +2964,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>4453000</v>
+        <v>61706000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Toshkent Plastik AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>355338252</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000762414867001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4706 31.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №175/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3010,38 +3005,38 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>4437000</v>
+        <v>3476000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8441</t>
+          <t>Оплата за товар по счет-фактуре №9421 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3049,28 +3044,33 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>2133000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Saodat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Предоплата за товар по договору №90/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
@@ -3087,31 +3087,31 @@
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>52235000</v>
+        <v>2053000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>300914599</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000769064736001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №17/26 от 03.08.2026</t>
+          <t>Оплата по с/ф №3836 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -3126,33 +3126,33 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>24607000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>12949000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>335820015</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000828621740001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4734 03.08.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №144/26</t>
         </is>
       </c>
     </row>
@@ -3167,23 +3167,23 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>6020000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>15019000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3193,14 +3193,14 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №256/26 от 03.08.2026</t>
+          <t>Оплата за сырье по дог. №275/26 от 03.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3210,21 +3210,21 @@
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>3184000</v>
+        <v>2148000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3234,14 +3234,14 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №754</t>
+          <t>Оплата за продукцию по договору №122/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3249,40 +3249,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>11483000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>3771000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Qo'qon Non MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>298553382</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000217624148001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №27/26</t>
+          <t>Оплата за товар по счет-фактуре №8208 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3290,23 +3290,18 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>5329000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>41844000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>244275303</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3316,7 +3311,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №51/26, QQS 12%</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №1594</t>
         </is>
       </c>
     </row>
@@ -3333,38 +3328,38 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>2948000</v>
+        <v>30145000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1254 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №168/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3372,23 +3367,23 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>32716000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>6652000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Oydin Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>245509421</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000549318625001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3398,14 +3393,14 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №299/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №264/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3414,34 +3409,39 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>41844000</v>
+        <v>3567000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Marg'ilon Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>373800074</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000143983689001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ISH HAQI TO'LOVI IYUL 2026 (PLASTIK KARTALARGA)</t>
+          <t>Ijara haqi avgust oyi uchun, shartnoma №63/21</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3450,39 +3450,39 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>3567000</v>
+        <v>6830000</v>
       </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Buxoro Qurilish Materiallari XK</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>273362210</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000002946212001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartnoma №49/20</t>
+          <t>Предоплата за материалы по дог. №158/26</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3491,32 +3491,32 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>81109000</v>
+        <v>7991000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oqtosh Metall MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>357211150</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000420711962001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №268/26</t>
+          <t>Оплата за сырье по дог. №164/26 от 10.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3531,23 +3531,23 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>8334000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>12609000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4690</t>
+          <t>Оплата за транспортные услуги по договору №68/26</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3574,38 +3574,38 @@
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>5273000</v>
+        <v>2321000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>335820015</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000828621740001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №39/26, QQS 12%</t>
+          <t>Shartnoma №10/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3614,32 +3614,32 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>14701000</v>
+        <v>6030000</v>
       </c>
       <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nukus Trans Servis XK</t>
+          <t>Qo'qon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>238308997</t>
+          <t>353385283</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000489728766001</t>
+          <t>20208000551531057001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №391</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №182/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -3654,40 +3654,40 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>62230000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>21953000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Qo'qon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>353385283</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000551531057001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6112 11.08.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №174/26 от 11.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3697,38 +3697,38 @@
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>26958000</v>
+        <v>7418000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Shodlik Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>382001558</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000862174052001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №1580 ОТ 11.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №1624 от 13.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,40 +3736,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>15010000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>5706000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №59/26, QQS 12%</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3777,40 +3777,40 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>9667000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>5706000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Shartnoma №199/26 bo'yicha oldindan to'lov</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>15.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3819,39 +3819,34 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>52687000</v>
+        <v>37900000</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Qo'qon Non MChJ</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>298553382</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-8940)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000217624148001</t>
+          <t>16307000367732556417</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7965</t>
+          <t>Kredit shartnomasi L-2025-8940 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3861,38 +3856,38 @@
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>10804000</v>
+        <v>3016000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8689</t>
+          <t>Оплата по с/ф №8798 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3900,40 +3895,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>22194000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>2230000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nukus Trans Servis XK</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>238308997</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000489728766001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8244</t>
+          <t>Оплата за товар по счет-фактуре №5862 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3941,40 +3936,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>4837000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>46408000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Shartnoma №167/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №3663</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3984,21 +3979,21 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>4266000</v>
+        <v>2173000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4008,14 +4003,14 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №294/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №4541 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4025,38 +4020,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>3914000</v>
+        <v>2864000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>300914599</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000769064736001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2820 14.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №3489 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>15.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4064,35 +4059,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>37900000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>2165000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-8940)</t>
+          <t>Namangan Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>16307000367732556417</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-8940 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Предоплата за товар по договору №113/26 от 19.08.2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4100,40 +4100,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>15545000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>12616000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9839</t>
+          <t>Оплата за товары согласно счет-фактуре №6332</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4143,21 +4143,21 @@
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>13577000</v>
+        <v>126235000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4167,14 +4167,14 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №717 17.08.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №8/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4182,40 +4182,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>5985000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>8012000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7228</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №60/26</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4223,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>5315000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>12584000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Olmaliq Tikuv MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>335820015</t>
+          <t>324142150</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000828621740001</t>
+          <t>20208000896637623001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №495 17.08.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №290/26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4266,21 +4266,21 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>4216000</v>
+        <v>14460000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4290,14 +4290,14 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8497 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №271/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4305,40 +4305,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>3469000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9149 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4347,39 +4347,39 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>5706000</v>
+        <v>14285000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Оплата за сырье по договору №220/26 от 21.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4387,40 +4387,40 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>5706000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>8570000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Оплата за продукцию по договору №59/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4428,40 +4428,40 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>12656000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>2627000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №176/26 от 17.08.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №4196 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,40 +4469,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>29716000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>2603000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №214/26</t>
+          <t>Оплата по счет-фактуре №7248 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4511,22 +4511,22 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>61926000</v>
+        <v>4894000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nukus Trans Servis XK</t>
+          <t>Olmaliq Tikuv MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>238308997</t>
+          <t>324142150</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000489728766001</t>
+          <t>20208000896637623001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4536,14 +4536,14 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №90/26</t>
+          <t>Оплата за сырье по дог. №256/26 от 24.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4551,40 +4551,40 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>64864000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>14995000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №100/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №1272</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4594,38 +4594,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>6719000</v>
+        <v>42519000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Omad Agro Servis MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>353455094</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000115493186001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8436 21.08.2026, QQS ilan</t>
+          <t>Оплата по с/ф №4192 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4635,38 +4635,38 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>3981000</v>
+        <v>8678000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №264/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №222/26 от 26.08.2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4674,40 +4674,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>7423000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>68690000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6499 24.08.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №1080</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4717,21 +4717,21 @@
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>3644000</v>
+        <v>26369000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>335820015</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000828621740001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4741,14 +4741,14 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1177</t>
+          <t>Оплата за продукцию по дог. №275/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4758,21 +4758,21 @@
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>2998000</v>
+        <v>11182000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4782,14 +4782,14 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9607</t>
+          <t>Оплата за товар по счет-фактуре №1840 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4797,40 +4797,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>5981000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>2034000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Yulduz Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>362287079</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000216223901001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>QQS IYUL 2026 UCHUN</t>
+          <t>Оплата за продукцию по договору №181/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4838,40 +4838,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>13370000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>2229000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000654034012001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №8915 25.08.2026, QQS BILAN</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4881,21 +4881,21 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>6574000</v>
+        <v>10204000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>335820015</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000828621740001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1222 25.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №38/26 от 28.08.2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4922,21 +4922,21 @@
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>5149000</v>
+        <v>5533000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4946,14 +4946,14 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №58/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1149</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4961,40 +4961,40 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>2229000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>4280000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000042275412001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Elektr eneriyasi uchun to'lov avgust</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9808 ОТ 31.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5002,40 +5002,40 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>22081000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>2347000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №211/26</t>
+          <t>Предоплата за товар по договору №159/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5043,40 +5043,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>12743000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>2282000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oqtosh Metall MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>357211150</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000420711962001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6275</t>
+          <t>Предоплата за товар по договору №223/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5084,40 +5084,35 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>10448000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>353047245</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6732</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5125,40 +5120,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>6903000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>5869000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №769 за поставленный товар</t>
+          <t>Оплата за сырье по дог. №115/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5166,23 +5161,23 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>22482000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>10841000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5192,14 +5187,14 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5055 28.08.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №125/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5207,33 +5202,33 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>7226000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>12811000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>300914599</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000769064736001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №95/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №252/26</t>
         </is>
       </c>
     </row>
@@ -5248,33 +5243,33 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>23353000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>25241000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №36/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №289/26</t>
         </is>
       </c>
     </row>
@@ -5289,40 +5284,40 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>10116000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>49497000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8208</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №137/26</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5332,21 +5327,21 @@
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>9470000</v>
+        <v>4093000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5356,14 +5351,14 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №11/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №258/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5371,35 +5366,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>3369000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Saodat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за товар по счет-фактуре №4199 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5408,39 +5408,39 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>30263000</v>
+        <v>5255000</v>
       </c>
       <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №25/26</t>
+          <t>Предоплата за материалы по договору №125/26</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5448,23 +5448,18 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n">
-        <v>9146000</v>
-      </c>
+      <c r="C130" s="2" t="n">
+        <v>38682000</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>300914599</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000769064736001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5474,14 +5469,14 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Shartnoma №105/26 bo'yicha oldindan to'lov</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №3843</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5489,40 +5484,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>20310000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>8074000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №217/26</t>
+          <t>Предоплата за товар по договору №160/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5530,28 +5525,33 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>38682000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>3940000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Saodat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за товар по счет-актуре №4909 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -5568,21 +5568,21 @@
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>15780000</v>
+        <v>3908000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>387355810</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000736865572001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №97/6, QQS 12%</t>
+          <t>Оплата по с/ф №1195 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -5607,40 +5607,40 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>35234000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>3212000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №18/26</t>
+          <t>Оплата за продукцию по дог. №97/6, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5648,33 +5648,33 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>23059000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>96566000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>335820015</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000828621740001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №286/26, НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №3470</t>
         </is>
       </c>
     </row>
@@ -5689,40 +5689,40 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>3297000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>5708000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Buxoro Qurilish Materiallari XK</t>
+          <t>Saodat Tikuv XK</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>273362210</t>
+          <t>336819568</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000002946212001</t>
+          <t>20208000185864459001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №49/20</t>
+          <t>Tovar uchun to'lov, h/f №2922 09.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5730,40 +5730,40 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>14696000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>3297000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Marg'ilon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>373800074</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000143983689001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Shartnoma №20/26 bo'yicha oldindan to'lov</t>
+          <t>Арендная плата за сентябрь 2026 г. по дог. №63/21</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5773,21 +5773,21 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>29580000</v>
+        <v>15624000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5797,14 +5797,14 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SHARTNOMA №22/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата по счет-фактуре №7226 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5812,40 +5812,40 @@
           <t>229</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>35070000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>8471000</v>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №270/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №3055 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5855,38 +5855,38 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>10908000</v>
+        <v>10038000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Oydin Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>245509421</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000549318625001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Shartnoma №174/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №5693 от 11.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5894,23 +5894,23 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>8976000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>28106000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5920,14 +5920,14 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Shartnoma №72/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №151/26 от 11.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5935,40 +5935,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>5275000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>37815000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>IJTIMOIY SOLIQ AVGUST 2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5779 14.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5976,40 +5976,40 @@
           <t>233</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>5275000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>12836000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Оплата за продукцию по договору №112/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6017,40 +6017,40 @@
           <t>234</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>23962000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>4689000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4532</t>
+          <t>Предоплата за товар по договору №85/26 от 14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6059,34 +6059,39 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>37900000</v>
+        <v>5275000</v>
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-8940)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>16307000367732556417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-8940 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6094,40 +6099,40 @@
           <t>236</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>78999000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>5275000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Shatnoma №156/26 bo'yicha oldindan to'lov</t>
+          <t>НДФЛ ЗА АВГУСТ 2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6136,39 +6141,39 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>15803000</v>
+        <v>112306000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo XK</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>356873558</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000087368655001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №126/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №4615</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6176,40 +6181,40 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>17848000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>8626000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Ishonch Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>276818296</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000373211477001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №261/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №134/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6217,23 +6222,23 @@
           <t>239</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>10989000</v>
-      </c>
+      <c r="C149" s="2" t="n">
+        <v>11798000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6243,14 +6248,14 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6001</t>
+          <t>Оплата за сырье по договору №151/26 от 15.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6258,23 +6263,23 @@
           <t>240</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>9613000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>17577000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6284,14 +6289,14 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3086 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №294/26</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6299,23 +6304,18 @@
           <t>241</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>8792000</v>
-      </c>
+      <c r="C151" s="2" t="n">
+        <v>37900000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>300914599</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-8940)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000769064736001</t>
+          <t>16307000367732556417</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6325,14 +6325,14 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9802 21.09.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-8940 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6342,38 +6342,38 @@
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>6223000</v>
+        <v>52026000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3150 за поставленный товар</t>
+          <t>Предоплата за товар по договору №63/26 от 16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6381,23 +6381,23 @@
           <t>243</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
-        <v>40994000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>6026000</v>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nukus Trans Servis XK</t>
+          <t>Shodlik Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>238308997</t>
+          <t>382001558</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000489728766001</t>
+          <t>20208000862174052001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6407,14 +6407,14 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2038</t>
+          <t>Mahsulot uchun t'lov, shartnoma №86/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6423,39 +6423,39 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>136879000</v>
+        <v>10207000</v>
       </c>
       <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Omad Dori-Darmon MChJ</t>
+          <t>Olmaliq Tikuv MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>263369653</t>
+          <t>324142150</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000352017875001</t>
+          <t>20208000896637623001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №316</t>
+          <t>Оплата за товары согласно счет-фактуре №6320</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6465,21 +6465,21 @@
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>36237000</v>
+        <v>3864000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6489,14 +6489,14 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3895 22.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №253/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6504,23 +6504,23 @@
           <t>246</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>7326000</v>
-      </c>
+      <c r="C156" s="2" t="n">
+        <v>5903000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6530,14 +6530,14 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №195/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №97/26</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6545,40 +6545,40 @@
           <t>247</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n">
-        <v>5461000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>48288000</v>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Оплата по с/ф №4825 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6588,38 +6588,38 @@
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>6455000</v>
+        <v>18476000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5257</t>
+          <t>Предоплата за товар по договору №220/26 от 18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6629,38 +6629,38 @@
       </c>
       <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="n">
-        <v>10024000</v>
+        <v>11168000</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Samarqand Oziq-ovqat Savdo MChJ</t>
+          <t>Bunyodkor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>244275303</t>
+          <t>314962079</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000524804055001</t>
+          <t>20208000897677627001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6216 28.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №56/26 от 18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6670,38 +6670,38 @@
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>9986000</v>
+        <v>15052000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Omad Agro Servis MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>353455094</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000115493186001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №275/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №206/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6711,38 +6711,38 @@
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>8585000</v>
+        <v>11095000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Bunyodkor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>335820015</t>
+          <t>314962079</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000828621740001</t>
+          <t>20208000897677627001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9138</t>
+          <t>Shartnoma №271/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6752,21 +6752,21 @@
       </c>
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="n">
-        <v>8157000</v>
+        <v>6804000</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>353047245</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000791042695001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6776,14 +6776,14 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №426 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №9616 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6791,40 +6791,40 @@
           <t>253</t>
         </is>
       </c>
-      <c r="C163" s="2" t="n">
-        <v>2061000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>4919000</v>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Namangan Polimer MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>291459977</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000042275412001</t>
+          <t>20208000906473613001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за товар по с/ф №9802 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6832,23 +6832,23 @@
           <t>254</t>
         </is>
       </c>
-      <c r="C164" s="2" t="n">
-        <v>42549000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>44107000</v>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Omad Dori-Darmon MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>263369653</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000352017875001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6858,14 +6858,14 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6335</t>
+          <t>Оплата за товар по с/ф №3895 от 22.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6875,38 +6875,38 @@
       </c>
       <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="n">
-        <v>123699000</v>
+        <v>19956000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>300914599</t>
+          <t>204724597</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000769064736001</t>
+          <t>20208000104269532001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №78/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №195/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6915,53 +6915,504 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>300000</v>
+        <v>4795000</v>
       </c>
       <c r="D166" s="2" t="n"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>355710452</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000179512678001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №252/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="n">
-        <v>1353001000</v>
-      </c>
-      <c r="D167" s="4" t="n">
-        <v>1372201000</v>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>5428000</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>НДС за август 2026 г.</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>16987000</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Qo'qon Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>353385283</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000551531057001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №202/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n">
+        <v>78109000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Guliston Yog'och MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>387355810</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000736865572001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №5257 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>5443000</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>355710452</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000179512678001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №2404</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>5418000</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Namangan Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>291459977</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000906473613001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Shartnoma №183/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>5286000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Saodat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>204724597</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000104269532001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №34/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>2061000</v>
+      </c>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000654034012001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>4759000</v>
+      </c>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>355710452</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000179512678001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №2115</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Qo'qon Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>353385283</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000551531057001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №165/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Yangi Asr Bank</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Комиссия за перевод</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>4350000</v>
+      </c>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Nukus Oziq-ovqat Savdo XK</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>355710452</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000179512678001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №44/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="n">
+        <v>1313544000</v>
+      </c>
+      <c r="D178" s="4" t="n">
+        <v>1332744000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C168" s="4" t="n">
+      <c r="C179" s="4" t="n">
         <v>194200000</v>
       </c>
-      <c r="D168" s="4" t="n"/>
+      <c r="D179" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
